--- a/data/trans_bre/P16A_n_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R2-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 17,53</t>
+          <t>2,79; 17,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,22; 24,39</t>
+          <t>8,67; 24,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 20,06</t>
+          <t>4,69; 19,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 18,46</t>
+          <t>4,29; 18,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,09; 127,22</t>
+          <t>10,93; 123,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,56; 116,15</t>
+          <t>29,49; 117,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,13; 130,54</t>
+          <t>21,24; 128,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,35; 82,62</t>
+          <t>14,07; 85,5</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 21,72</t>
+          <t>11,94; 22,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,44; 21,61</t>
+          <t>9,56; 22,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 20,25</t>
+          <t>8,68; 20,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 18,91</t>
+          <t>6,86; 19,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,36; 188,99</t>
+          <t>73,87; 197,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,79; 93,25</t>
+          <t>32,36; 98,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,96; 100,48</t>
+          <t>33,5; 102,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,05; 86,3</t>
+          <t>23,74; 87,11</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 16,55</t>
+          <t>4,01; 15,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 22,05</t>
+          <t>6,22; 21,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 13,77</t>
+          <t>0,96; 13,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 15,09</t>
+          <t>2,0; 14,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,27; 136,33</t>
+          <t>17,75; 118,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,53; 85,23</t>
+          <t>17,66; 83,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 73,31</t>
+          <t>4,84; 75,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 48,23</t>
+          <t>5,04; 49,74</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 20,04</t>
+          <t>8,5; 20,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,69; 27,46</t>
+          <t>13,31; 27,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 21,14</t>
+          <t>6,79; 20,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 13,83</t>
+          <t>-11,77; 13,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,85; 132,66</t>
+          <t>40,58; 138,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,04; 129,3</t>
+          <t>46,95; 131,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,07; 81,14</t>
+          <t>20,27; 75,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 43,53</t>
+          <t>-32,34; 44,7</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,43; 29,79</t>
+          <t>11,72; 28,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,73; 35,16</t>
+          <t>17,14; 35,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,79; 33,1</t>
+          <t>17,41; 34,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 17,41</t>
+          <t>-11,38; 17,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,0; 252,46</t>
+          <t>59,42; 236,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,25; 161,15</t>
+          <t>52,15; 156,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,07; 215,74</t>
+          <t>72,99; 229,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 62,44</t>
+          <t>-32,32; 64,04</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,89; 18,53</t>
+          <t>4,41; 18,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 20,12</t>
+          <t>3,3; 20,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,35; 17,02</t>
+          <t>1,65; 17,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 14,85</t>
+          <t>-0,65; 13,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,02; 120,36</t>
+          <t>18,9; 132,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,13; 71,99</t>
+          <t>9,04; 71,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,4; 95,82</t>
+          <t>4,9; 99,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 44,65</t>
+          <t>-1,5; 40,07</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 15,71</t>
+          <t>6,33; 15,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,35; 18,76</t>
+          <t>8,29; 18,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,63; 13,46</t>
+          <t>3,58; 13,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 42,78</t>
+          <t>7,38; 46,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,24; 102,82</t>
+          <t>31,98; 101,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,4; 84,75</t>
+          <t>30,59; 83,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,29; 71,42</t>
+          <t>14,73; 70,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,76; 147,76</t>
+          <t>20,4; 148,0</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,38; 13,98</t>
+          <t>5,12; 13,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,21; 14,31</t>
+          <t>5,62; 14,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,12; 15,19</t>
+          <t>5,99; 15,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,35; 29,34</t>
+          <t>11,01; 29,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,91; 75,12</t>
+          <t>22,07; 75,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,38; 76,67</t>
+          <t>23,41; 78,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,76; 68,61</t>
+          <t>22,42; 68,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,15; 326,95</t>
+          <t>45,4; 338,45</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,13; 14,29</t>
+          <t>10,28; 14,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,36; 17,04</t>
+          <t>12,7; 17,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,77; 14,15</t>
+          <t>9,81; 14,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,26; 25,61</t>
+          <t>9,57; 26,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>56,07; 87,17</t>
+          <t>55,17; 85,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,57; 70,25</t>
+          <t>47,83; 70,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,84; 64,91</t>
+          <t>40,75; 65,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31,04; 102,23</t>
+          <t>32,27; 106,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A_n_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,06</t>
+          <t>9,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 17,29</t>
+          <t>2,44; 16,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,67; 24,6</t>
+          <t>8,77; 24,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 19,54</t>
+          <t>5,37; 19,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 18,61</t>
+          <t>3,53; 15,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,93; 123,33</t>
+          <t>13,11; 121,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,49; 117,22</t>
+          <t>30,95; 117,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,24; 128,03</t>
+          <t>23,51; 129,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 85,5</t>
+          <t>12,47; 70,38</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,33</t>
+          <t>12,55</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 22,44</t>
+          <t>11,54; 21,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,56; 22,16</t>
+          <t>9,37; 22,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,68; 20,53</t>
+          <t>8,25; 20,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 19,0</t>
+          <t>6,66; 18,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,87; 197,82</t>
+          <t>72,73; 192,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,36; 98,77</t>
+          <t>31,85; 98,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,5; 102,09</t>
+          <t>31,86; 101,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,74; 87,11</t>
+          <t>23,38; 82,87</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,7</t>
+          <t>8,13</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 15,87</t>
+          <t>4,31; 16,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 21,72</t>
+          <t>5,83; 20,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 13,87</t>
+          <t>0,3; 13,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 14,95</t>
+          <t>1,46; 14,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,75; 118,86</t>
+          <t>20,94; 125,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,66; 83,09</t>
+          <t>17,82; 80,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 75,02</t>
+          <t>0,93; 74,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 49,74</t>
+          <t>2,76; 46,74</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>12,56</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 20,64</t>
+          <t>8,16; 20,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 27,57</t>
+          <t>13,45; 26,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 20,57</t>
+          <t>7,03; 21,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 13,93</t>
+          <t>4,24; 20,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,58; 138,25</t>
+          <t>36,49; 135,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,95; 131,88</t>
+          <t>45,94; 125,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,27; 75,52</t>
+          <t>20,74; 81,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 44,7</t>
+          <t>11,29; 75,99</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,71</t>
+          <t>14,93</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,72; 28,88</t>
+          <t>12,07; 28,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,14; 35,07</t>
+          <t>16,7; 35,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,41; 34,68</t>
+          <t>16,76; 33,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 17,7</t>
+          <t>7,52; 21,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,42; 236,92</t>
+          <t>60,42; 235,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,15; 156,06</t>
+          <t>51,08; 157,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,99; 229,0</t>
+          <t>70,86; 211,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 64,04</t>
+          <t>23,11; 94,06</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,74</t>
+          <t>7,72</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 18,48</t>
+          <t>3,91; 18,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,3; 20,22</t>
+          <t>3,26; 20,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 17,2</t>
+          <t>1,83; 16,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 13,55</t>
+          <t>0,34; 14,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,9; 132,63</t>
+          <t>17,3; 135,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,04; 71,79</t>
+          <t>9,14; 72,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,9; 99,9</t>
+          <t>7,69; 93,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 40,07</t>
+          <t>0,92; 43,92</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23,07</t>
+          <t>8,48</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 15,58</t>
+          <t>5,79; 15,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,29; 18,24</t>
+          <t>8,47; 18,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 13,5</t>
+          <t>3,93; 13,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,38; 46,39</t>
+          <t>2,67; 13,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,98; 101,42</t>
+          <t>29,45; 102,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,59; 83,61</t>
+          <t>31,66; 86,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,73; 70,55</t>
+          <t>16,4; 73,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,4; 148,0</t>
+          <t>6,77; 41,98</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18,33</t>
+          <t>12,04</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>106,83%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,12; 13,81</t>
+          <t>5,05; 14,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,62; 14,82</t>
+          <t>5,43; 14,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,99; 15,39</t>
+          <t>5,87; 15,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,01; 29,27</t>
+          <t>8,05; 16,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,07; 75,79</t>
+          <t>22,51; 76,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,41; 78,47</t>
+          <t>23,64; 80,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,42; 68,76</t>
+          <t>21,36; 67,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>45,4; 338,45</t>
+          <t>33,4; 81,57</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14,96</t>
+          <t>10,82</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,28; 14,27</t>
+          <t>10,24; 14,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,7; 17,22</t>
+          <t>12,46; 17,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,81; 14,21</t>
+          <t>9,57; 13,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,57; 26,2</t>
+          <t>8,66; 12,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55,17; 85,78</t>
+          <t>56,14; 86,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,83; 70,69</t>
+          <t>47,26; 70,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,75; 65,39</t>
+          <t>39,75; 63,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32,27; 106,48</t>
+          <t>27,89; 45,39</t>
         </is>
       </c>
     </row>
